--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_28-05-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_28-05-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA0A8E6-F773-447B-835B-16A300BF9C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421C7FCD-34DB-4544-A197-DD18C14C9EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28950" yWindow="1875" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4125" yWindow="1080" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1380,7 +1380,7 @@
         <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
         <v>51</v>
@@ -1828,7 +1828,7 @@
         <v>154</v>
       </c>
       <c r="E12" t="s">
-        <v>154</v>
+        <v>27</v>
       </c>
       <c r="F12" t="s">
         <v>155</v>
@@ -1940,7 +1940,7 @@
         <v>178</v>
       </c>
       <c r="E14" t="s">
-        <v>178</v>
+        <v>27</v>
       </c>
       <c r="F14" t="s">
         <v>179</v>
@@ -1996,7 +1996,7 @@
         <v>191</v>
       </c>
       <c r="E15" t="s">
-        <v>191</v>
+        <v>27</v>
       </c>
       <c r="F15" t="s">
         <v>192</v>
@@ -2108,7 +2108,7 @@
         <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F17" t="s">
         <v>27</v>
@@ -2164,7 +2164,7 @@
         <v>218</v>
       </c>
       <c r="E18" t="s">
-        <v>218</v>
+        <v>27</v>
       </c>
       <c r="F18" t="s">
         <v>27</v>
@@ -2220,7 +2220,7 @@
         <v>226</v>
       </c>
       <c r="E19" t="s">
-        <v>226</v>
+        <v>27</v>
       </c>
       <c r="F19" t="s">
         <v>27</v>
@@ -2276,7 +2276,7 @@
         <v>234</v>
       </c>
       <c r="E20" t="s">
-        <v>234</v>
+        <v>27</v>
       </c>
       <c r="F20" t="s">
         <v>27</v>
@@ -2332,7 +2332,7 @@
         <v>238</v>
       </c>
       <c r="E21" t="s">
-        <v>238</v>
+        <v>27</v>
       </c>
       <c r="F21" t="s">
         <v>27</v>
@@ -2388,7 +2388,7 @@
         <v>242</v>
       </c>
       <c r="E22" t="s">
-        <v>242</v>
+        <v>27</v>
       </c>
       <c r="F22" t="s">
         <v>27</v>
